--- a/Excel/13. Dynamic_Dashboard/Advance_Pivot_with_3d_and_Dyanamic_Dashboarding.xlsx
+++ b/Excel/13. Dynamic_Dashboard/Advance_Pivot_with_3d_and_Dyanamic_Dashboarding.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DC_DDS_02\Excel\13. Dynamic_Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DC_DDS_04\Excel\13. Dynamic_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD690F8-1800-4086-93A8-FC35442A1034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B314468-2E2E-4953-A286-36A7DB3756E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="4" xr2:uid="{2EEDDA8A-1E0B-4C35-B98E-5809934422EC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" firstSheet="1" activeTab="6" xr2:uid="{2EEDDA8A-1E0B-4C35-B98E-5809934422EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivot_1" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Pivot_4" sheetId="6" r:id="rId4"/>
     <sheet name="Dashboard" sheetId="7" r:id="rId5"/>
     <sheet name="Production Dataset" sheetId="1" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Production Dataset'!$A$1:$K$121</definedName>
@@ -29,15 +30,15 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="11" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId8"/>
         <x14:slicerCache r:id="rId9"/>
         <x14:slicerCache r:id="rId10"/>
         <x14:slicerCache r:id="rId11"/>
+        <x14:slicerCache r:id="rId12"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="55">
   <si>
     <t>ProductionID</t>
   </si>
@@ -216,6 +217,18 @@
   <si>
     <t>Production Dynamic Dashboard</t>
   </si>
+  <si>
+    <t>Sum of Production Cost Per Unit</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
 </sst>
 </file>
 
@@ -225,7 +238,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,6 +262,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -277,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -298,6 +317,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5662,6 +5682,518 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Advance_Pivot_with_3d_and_Dyanamic_Dashboarding.xlsx]Sheet1!PivotTable5</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="1" u="none">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>For 'Region: West', 'Age Groups': A2 has noticeably higher 'Production Cost Per Unit'.</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="D2D2D2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="ED7331"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="D2D2D2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ED7331"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-4BD3-47E5-A87E-BD717407B591}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$5:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>A2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>A1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>A3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$5:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>3292.0443218674632</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1990.3162868364366</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1519.2978086475678</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4BD3-47E5-A87E-BD717407B591}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="33"/>
+        <c:overlap val="-30"/>
+        <c:axId val="1774967776"/>
+        <c:axId val="1774968256"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1774967776"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="0" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Age Groups</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1774968256"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1774968256"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t>Production Cost Per Unit</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="1" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1774967776"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -5982,6 +6514,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="347">
   <cs:axisTitle>
@@ -9662,6 +10234,511 @@
       <cs:styleClr val="auto"/>
     </cs:lnRef>
     <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -10637,8 +11714,49 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1" descr="Chart type: Clustered Bar. For 'Region: West', 'Age Groups': A2 has noticeably higher 'Production Cost Per Unit'.&#10;&#10;Description automatically generated">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBAB6E3E-FBDD-C942-7433-BE8B24A4D826}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="ADMIN" refreshedDate="45908.898374189812" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="120" xr:uid="{0F094045-FCEF-4327-AFF9-5D21F622E5CE}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="ADMIN" refreshedDate="45994.563236226852" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="120" xr:uid="{0F094045-FCEF-4327-AFF9-5D21F622E5CE}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:K121" sheet="Production Dataset"/>
   </cacheSource>
@@ -12426,7 +13544,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9911DA61-3A53-4D17-9420-F68C4ED68E59}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9911DA61-3A53-4D17-9420-F68C4ED68E59}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -12662,7 +13780,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E073E34A-43F4-42E5-8244-1F456AF4C22B}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E073E34A-43F4-42E5-8244-1F456AF4C22B}" name="PivotTable2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
   <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -12905,7 +14023,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D78E9B3-EF8A-4596-876F-BE3FD6627AE3}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D78E9B3-EF8A-4596-876F-BE3FD6627AE3}" name="PivotTable3" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -13153,7 +14271,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38820309-D752-4526-9EA5-75FC3A1582F1}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38820309-D752-4526-9EA5-75FC3A1582F1}" name="PivotTable4" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -13552,6 +14670,220 @@
           </reference>
           <reference field="4" count="1" selected="0">
             <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E90D500-1E81-4C7E-B18C-F91D7AF7FFD0}" name="PivotTable5" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A4:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="14" outline="0" showAll="0">
+      <items count="100">
+        <item x="45"/>
+        <item x="51"/>
+        <item x="63"/>
+        <item x="28"/>
+        <item x="43"/>
+        <item x="3"/>
+        <item x="15"/>
+        <item x="48"/>
+        <item x="8"/>
+        <item x="37"/>
+        <item x="44"/>
+        <item x="33"/>
+        <item x="60"/>
+        <item x="94"/>
+        <item x="46"/>
+        <item x="23"/>
+        <item x="95"/>
+        <item x="86"/>
+        <item x="58"/>
+        <item x="32"/>
+        <item x="40"/>
+        <item x="18"/>
+        <item x="90"/>
+        <item x="89"/>
+        <item x="97"/>
+        <item x="85"/>
+        <item x="77"/>
+        <item x="82"/>
+        <item x="26"/>
+        <item x="74"/>
+        <item x="52"/>
+        <item x="81"/>
+        <item x="20"/>
+        <item x="22"/>
+        <item x="7"/>
+        <item x="19"/>
+        <item x="72"/>
+        <item x="70"/>
+        <item x="69"/>
+        <item x="14"/>
+        <item x="76"/>
+        <item x="71"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="80"/>
+        <item x="73"/>
+        <item x="5"/>
+        <item x="61"/>
+        <item x="64"/>
+        <item x="98"/>
+        <item x="47"/>
+        <item x="68"/>
+        <item x="93"/>
+        <item x="30"/>
+        <item x="54"/>
+        <item x="96"/>
+        <item x="34"/>
+        <item x="56"/>
+        <item x="0"/>
+        <item x="16"/>
+        <item x="91"/>
+        <item x="57"/>
+        <item x="87"/>
+        <item x="13"/>
+        <item x="38"/>
+        <item x="11"/>
+        <item x="88"/>
+        <item x="1"/>
+        <item x="31"/>
+        <item x="39"/>
+        <item x="78"/>
+        <item x="55"/>
+        <item x="75"/>
+        <item x="4"/>
+        <item x="41"/>
+        <item x="53"/>
+        <item x="67"/>
+        <item x="42"/>
+        <item x="83"/>
+        <item x="12"/>
+        <item x="35"/>
+        <item x="17"/>
+        <item x="6"/>
+        <item x="65"/>
+        <item x="36"/>
+        <item x="84"/>
+        <item x="2"/>
+        <item x="62"/>
+        <item x="9"/>
+        <item x="49"/>
+        <item x="25"/>
+        <item x="21"/>
+        <item x="79"/>
+        <item x="92"/>
+        <item x="24"/>
+        <item x="59"/>
+        <item x="29"/>
+        <item x="66"/>
+        <item x="50"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="2"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" compact="0" numFmtId="1" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Production Cost Per Unit" fld="10" baseField="0" baseItem="0" numFmtId="1"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
@@ -18835,4 +20167,70 @@
   <autoFilter ref="A1:K121" xr:uid="{11EB702C-2CA7-4800-A1A0-B4816E9E0C16}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB09558B-4556-4564-A003-8D20A8ACB316}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="12"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="3">
+        <v>3292.0443218674632</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1990.3162868364366</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1519.2978086475678</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="3">
+        <v>6801.6584173514675</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Excel/13. Dynamic_Dashboard/Advance_Pivot_with_3d_and_Dyanamic_Dashboarding.xlsx
+++ b/Excel/13. Dynamic_Dashboard/Advance_Pivot_with_3d_and_Dyanamic_Dashboarding.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DC_DDS_04\Excel\13. Dynamic_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B314468-2E2E-4953-A286-36A7DB3756E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EE0A79-F40B-426D-8C02-0947940F1966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" firstSheet="1" activeTab="6" xr2:uid="{2EEDDA8A-1E0B-4C35-B98E-5809934422EC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" firstSheet="1" activeTab="4" xr2:uid="{2EEDDA8A-1E0B-4C35-B98E-5809934422EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivot_1" sheetId="2" r:id="rId1"/>
@@ -23,27 +23,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Production Dataset'!$A$1:$K$121</definedName>
-    <definedName name="Slicer_Age_Groups">#N/A</definedName>
-    <definedName name="Slicer_Gender">#N/A</definedName>
-    <definedName name="Slicer_Quarters__ProductionDate">#N/A</definedName>
-    <definedName name="Slicer_Region">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="11" r:id="rId8"/>
+    <pivotCache cacheId="9" r:id="rId8"/>
   </pivotCaches>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
-      <x14:slicerCaches>
-        <x14:slicerCache r:id="rId9"/>
-        <x14:slicerCache r:id="rId10"/>
-        <x14:slicerCache r:id="rId11"/>
-        <x14:slicerCache r:id="rId12"/>
-      </x14:slicerCaches>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
-      <x14:workbookPr/>
-    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -63,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="57">
   <si>
     <t>ProductionID</t>
   </si>
@@ -229,6 +214,12 @@
   <si>
     <t>A3</t>
   </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
 </sst>
 </file>
 
@@ -310,6 +301,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -317,12 +309,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
+    <dxf>
+      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
@@ -596,16 +599,16 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>251290</c:v>
+                  <c:v>1152805</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>98825</c:v>
+                  <c:v>604575</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>159368</c:v>
+                  <c:v>703282</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>259321</c:v>
+                  <c:v>910416</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1185,23 +1188,77 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Pivot_2!$A$4:$A$5</c:f>
+              <c:f>Pivot_2!$A$4:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
+                  <c:v>Andrew Blue</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Chris Green</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>David White</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Emily Davis</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Jane Smith</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>John Doe</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Laura Black</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Mike Brown</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Nancy Grey</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Sarah Lee</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Pivot_2!$B$4:$B$5</c:f>
+              <c:f>Pivot_2!$B$4:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1672,9 +1729,9 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Pivot_3!$A$4:$A$16</c:f>
+              <c:f>Pivot_3!$A$4:$A$19</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="13"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>Sep</c:v>
@@ -1706,6 +1763,15 @@
                   <c:pt idx="9">
                     <c:v>Jun</c:v>
                   </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Jul</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Aug</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Sep</c:v>
+                  </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
@@ -1720,39 +1786,48 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Pivot_3!$B$4:$B$16</c:f>
+              <c:f>Pivot_3!$B$4:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>213</c:v>
+                  <c:v>771</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1172</c:v>
+                  <c:v>3103</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>126</c:v>
+                  <c:v>4803</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1221</c:v>
+                  <c:v>2494</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>837</c:v>
+                  <c:v>3026</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1318</c:v>
+                  <c:v>4127</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>866</c:v>
+                  <c:v>3875</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>155</c:v>
+                  <c:v>1528</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>430</c:v>
+                  <c:v>1684</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>811</c:v>
+                  <c:v>3537</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1536</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2864</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1379</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2502,16 +2577,16 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>113.14090538681076</c:v>
+                  <c:v>140.87387695413258</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>160.50876012499171</c:v>
+                  <c:v>108.368246516667</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>257.48917478225388</c:v>
+                  <c:v>180.4410334877862</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>93.29276767399233</c:v>
+                  <c:v>108.97659894637712</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3026,16 +3101,16 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>251290</c:v>
+                  <c:v>1152805</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>98825</c:v>
+                  <c:v>604575</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>159368</c:v>
+                  <c:v>703282</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>259321</c:v>
+                  <c:v>910416</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3729,23 +3804,77 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Pivot_2!$A$4:$A$5</c:f>
+              <c:f>Pivot_2!$A$4:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
+                  <c:v>Andrew Blue</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Chris Green</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>David White</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Emily Davis</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Jane Smith</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>John Doe</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Laura Black</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Mike Brown</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Nancy Grey</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Sarah Lee</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Pivot_2!$B$4:$B$5</c:f>
+              <c:f>Pivot_2!$B$4:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4430,9 +4559,9 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Pivot_3!$A$4:$A$16</c:f>
+              <c:f>Pivot_3!$A$4:$A$19</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="13"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>Sep</c:v>
@@ -4464,6 +4593,15 @@
                   <c:pt idx="9">
                     <c:v>Jun</c:v>
                   </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Jul</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Aug</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Sep</c:v>
+                  </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
@@ -4478,39 +4616,48 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Pivot_3!$B$4:$B$16</c:f>
+              <c:f>Pivot_3!$B$4:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>213</c:v>
+                  <c:v>771</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1172</c:v>
+                  <c:v>3103</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>126</c:v>
+                  <c:v>4803</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1221</c:v>
+                  <c:v>2494</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>837</c:v>
+                  <c:v>3026</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1318</c:v>
+                  <c:v>4127</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>866</c:v>
+                  <c:v>3875</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>155</c:v>
+                  <c:v>1528</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>430</c:v>
+                  <c:v>1684</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>811</c:v>
+                  <c:v>3537</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1536</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2864</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1379</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5580,16 +5727,16 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>113.14090538681076</c:v>
+                  <c:v>140.87387695413258</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>160.50876012499171</c:v>
+                  <c:v>108.368246516667</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>257.48917478225388</c:v>
+                  <c:v>180.4410334877862</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>93.29276767399233</c:v>
+                  <c:v>108.97659894637712</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11397,318 +11544,6 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>106679</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="6" name="Region">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C568A6B-3188-CD8E-01D4-2B48F14A2241}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Region"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="571500" y="845820"/>
-              <a:ext cx="1828800" cy="1613534"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-IN" sz="1100"/>
-                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>60960</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>144781</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>60960</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>91441</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="7" name="Gender">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6028A87A-4C8B-9492-2112-EBD39604E52E}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Gender"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2499360" y="868681"/>
-              <a:ext cx="1828800" cy="1575435"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-IN" sz="1100"/>
-                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>251460</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>129541</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>251460</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>60961</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="8" name="Age Groups">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAAD1CA8-D90A-C203-77F3-CBFC18E4C7BA}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Age Groups"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6347460" y="853441"/>
-              <a:ext cx="1828800" cy="1560195"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-IN" sz="1100"/>
-                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>106681</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="9" name="Quarters (ProductionDate)">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F98AB570-3CE5-7301-E799-B19975011255}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Quarters (ProductionDate)"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4419600" y="830581"/>
-              <a:ext cx="1828800" cy="1590674"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-IN" sz="1100"/>
-                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -13544,7 +13379,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9911DA61-3A53-4D17-9420-F68C4ED68E59}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9911DA61-3A53-4D17-9420-F68C4ED68E59}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -13669,8 +13504,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
+        <item x="0"/>
+        <item x="2"/>
         <item x="1"/>
         <item t="default"/>
       </items>
@@ -13743,7 +13578,7 @@
     <dataField name="Total Cost" fld="6" baseField="4" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
+    <format dxfId="7">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13780,8 +13615,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E073E34A-43F4-42E5-8244-1F456AF4C22B}" name="PivotTable2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
-  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E073E34A-43F4-42E5-8244-1F456AF4C22B}" name="PivotTable2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+  <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -13926,8 +13761,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
+        <item x="0"/>
+        <item x="2"/>
         <item x="1"/>
         <item t="default"/>
       </items>
@@ -13954,12 +13789,12 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="7">
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
         <item x="3"/>
-        <item h="1" x="4"/>
-        <item h="1" x="5"/>
+        <item x="4"/>
+        <item x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13976,9 +13811,36 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
     <i>
       <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
     </i>
     <i t="grand">
       <x/>
@@ -14023,8 +13885,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D78E9B3-EF8A-4596-876F-BE3FD6627AE3}" name="PivotTable3" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D78E9B3-EF8A-4596-876F-BE3FD6627AE3}" name="PivotTable3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="A3:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -14140,8 +14002,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
+        <item x="0"/>
+        <item x="2"/>
         <item x="1"/>
         <item t="default"/>
       </items>
@@ -14191,7 +14053,7 @@
     <field x="13"/>
     <field x="11"/>
   </rowFields>
-  <rowItems count="13">
+  <rowItems count="16">
     <i>
       <x v="1"/>
     </i>
@@ -14227,6 +14089,15 @@
     </i>
     <i r="1">
       <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
     </i>
     <i t="grand">
       <x/>
@@ -14271,7 +14142,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38820309-D752-4526-9EA5-75FC3A1582F1}" name="PivotTable4" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38820309-D752-4526-9EA5-75FC3A1582F1}" name="PivotTable4" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -14396,8 +14267,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
+        <item x="0"/>
+        <item x="2"/>
         <item x="1"/>
         <item t="default"/>
       </items>
@@ -14441,7 +14312,7 @@
     <dataField name="Average of Production Cost Per Unit" fld="10" subtotal="average" baseField="4" baseItem="0" numFmtId="43"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="2">
+    <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14688,7 +14559,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E90D500-1E81-4C7E-B18C-F91D7AF7FFD0}" name="PivotTable5" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E90D500-1E81-4C7E-B18C-F91D7AF7FFD0}" name="PivotTable5" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
   <location ref="A4:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -14899,90 +14770,6 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
-</file>
-
-<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Region" xr10:uid="{8DEE30BA-F742-41C9-9BB0-7354A6A2AB05}" sourceName="Region">
-  <pivotTables>
-    <pivotTable tabId="3" name="PivotTable2"/>
-  </pivotTables>
-  <data>
-    <tabular pivotCacheId="1603146037">
-      <items count="4">
-        <i x="1" s="1"/>
-        <i x="3" s="1" nd="1"/>
-        <i x="2" s="1" nd="1"/>
-        <i x="0" s="1" nd="1"/>
-      </items>
-    </tabular>
-  </data>
-</slicerCacheDefinition>
-</file>
-
-<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Gender" xr10:uid="{5EA84ADD-EA31-46BC-BA0F-C51F5D58233C}" sourceName="Gender">
-  <pivotTables>
-    <pivotTable tabId="3" name="PivotTable2"/>
-  </pivotTables>
-  <data>
-    <tabular pivotCacheId="1603146037">
-      <items count="3">
-        <i x="0" s="1"/>
-        <i x="1" s="1" nd="1"/>
-        <i x="2" s="1" nd="1"/>
-      </items>
-    </tabular>
-  </data>
-</slicerCacheDefinition>
-</file>
-
-<file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Age_Groups" xr10:uid="{8F18D21F-A306-46D8-ABB3-459D593C50AD}" sourceName="Age Groups">
-  <pivotTables>
-    <pivotTable tabId="3" name="PivotTable2"/>
-    <pivotTable tabId="2" name="PivotTable1"/>
-    <pivotTable tabId="4" name="PivotTable3"/>
-    <pivotTable tabId="6" name="PivotTable4"/>
-  </pivotTables>
-  <data>
-    <tabular pivotCacheId="1603146037">
-      <items count="3">
-        <i x="0"/>
-        <i x="2"/>
-        <i x="1" s="1"/>
-      </items>
-    </tabular>
-  </data>
-</slicerCacheDefinition>
-</file>
-
-<file path=xl/slicerCaches/slicerCache4.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Quarters__ProductionDate" xr10:uid="{73CB2F42-7235-4E4A-8175-F579F6DF34C4}" sourceName="Quarters (ProductionDate)">
-  <pivotTables>
-    <pivotTable tabId="3" name="PivotTable2"/>
-  </pivotTables>
-  <data>
-    <tabular pivotCacheId="1603146037">
-      <items count="6">
-        <i x="1"/>
-        <i x="2"/>
-        <i x="3" s="1"/>
-        <i x="4"/>
-        <i x="0" nd="1"/>
-        <i x="5" nd="1"/>
-      </items>
-    </tabular>
-  </data>
-</slicerCacheDefinition>
-</file>
-
-<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Region" xr10:uid="{BA0B1FD9-BC7C-4156-9EE4-E560344C0918}" cache="Slicer_Region" caption="Region" rowHeight="247650"/>
-  <slicer name="Gender" xr10:uid="{CCA25CEF-59AE-4A6A-A211-BF9D55E51F69}" cache="Slicer_Gender" caption="Gender" rowHeight="247650"/>
-  <slicer name="Age Groups" xr10:uid="{608BB628-D08F-430A-8116-E683697DD9A6}" cache="Slicer_Age_Groups" caption="Age Groups" rowHeight="247650"/>
-  <slicer name="Quarters (ProductionDate)" xr10:uid="{52D16B65-26BB-4E77-B06B-14049865121E}" cache="Slicer_Quarters__ProductionDate" caption="Quarters (ProductionDate)" startItem="2" rowHeight="247650"/>
-</slicers>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15306,7 +15093,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -15322,7 +15109,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="7">
-        <v>251290</v>
+        <v>1152805</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -15330,7 +15117,7 @@
         <v>27</v>
       </c>
       <c r="B5" s="7">
-        <v>98825</v>
+        <v>604575</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -15338,7 +15125,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="7">
-        <v>159368</v>
+        <v>703282</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -15346,7 +15133,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="7">
-        <v>259321</v>
+        <v>910416</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -15354,7 +15141,7 @@
         <v>33</v>
       </c>
       <c r="B8" s="7">
-        <v>768804</v>
+        <v>3371078</v>
       </c>
     </row>
   </sheetData>
@@ -15365,7 +15152,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F29BA515-52AE-4B4C-A15C-1102C3846F32}">
-  <dimension ref="A3:B5"/>
+  <dimension ref="A3:B14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -15382,18 +15169,90 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="11">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="B4" s="12">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="12">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="11">
-        <v>1</v>
+      <c r="B14" s="12">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -15404,7 +15263,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1C5026-84D1-4491-A97E-2758840F31F6}">
-  <dimension ref="A3:B16"/>
+  <dimension ref="A3:B19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -15423,104 +15282,128 @@
       <c r="A4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="11">
-        <v>2732</v>
+      <c r="B4" s="12">
+        <v>11171</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="11">
-        <v>213</v>
+      <c r="B5" s="12">
+        <v>771</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="11">
-        <v>1172</v>
+      <c r="B6" s="12">
+        <v>3103</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="11">
-        <v>126</v>
+      <c r="B7" s="12">
+        <v>4803</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="11">
-        <v>1221</v>
+      <c r="B8" s="12">
+        <v>2494</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="11">
-        <v>4417</v>
+      <c r="B9" s="12">
+        <v>23556</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="11">
-        <v>837</v>
+      <c r="B10" s="12">
+        <v>3026</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="11">
-        <v>1318</v>
+      <c r="B11" s="12">
+        <v>4127</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="11">
-        <v>866</v>
+      <c r="B12" s="12">
+        <v>3875</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="11">
-        <v>155</v>
+      <c r="B13" s="12">
+        <v>1528</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="11">
-        <v>430</v>
+      <c r="B14" s="12">
+        <v>1684</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="11">
-        <v>811</v>
+      <c r="B15" s="12">
+        <v>3537</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="12">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="12">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="12">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="11">
-        <v>7149</v>
+      <c r="B19" s="12">
+        <v>34727</v>
       </c>
     </row>
   </sheetData>
@@ -15552,7 +15435,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="6">
-        <v>113.14090538681076</v>
+        <v>140.87387695413258</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -15560,7 +15443,7 @@
         <v>27</v>
       </c>
       <c r="B5" s="6">
-        <v>160.50876012499171</v>
+        <v>108.368246516667</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -15568,7 +15451,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="6">
-        <v>257.48917478225388</v>
+        <v>180.4410334877862</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -15576,7 +15459,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="6">
-        <v>93.29276767399233</v>
+        <v>108.97659894637712</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -15584,7 +15467,7 @@
         <v>33</v>
       </c>
       <c r="B8" s="6">
-        <v>129.00151070623102</v>
+        <v>132.39235089555021</v>
       </c>
     </row>
   </sheetData>
@@ -15599,70 +15482,70 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -15670,13 +15553,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
-      <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
-      </x14:slicerList>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -20179,7 +20055,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="12"/>
+      <c r="A1" s="9"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
